--- a/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-identity-reliability-supplement.xlsx
+++ b/fix/issue-298-identity-status-rniv/ig/CodeSystem-fr-core-cs-identity-reliability-supplement.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T15:42:07+00:00</t>
+    <t>2026-08-07T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
